--- a/data/trans_orig/Q23_tabaco_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40154</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65987</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55574</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84405</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153738</t>
+          <t>155222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179571</t>
+          <t>180431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>85160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101509</t>
+          <t>101113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247296</t>
+          <t>246449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>276127</t>
+          <t>276494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67087</t>
+          <t>66246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>30718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>51020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77366</t>
+          <t>74304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>110149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118561</t>
+          <t>119402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145144</t>
+          <t>144651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106833</t>
+          <t>107557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128844</t>
+          <t>127859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234100</t>
+          <t>234076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266859</t>
+          <t>269921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87285</t>
+          <t>88609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121503</t>
+          <t>120657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99086</t>
+          <t>98383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133491</t>
+          <t>134494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184227</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218445</t>
+          <t>217121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>41627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54281</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233244</t>
+          <t>232241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267649</t>
+          <t>268352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>244915</t>
+          <t>243544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296519</t>
+          <t>295242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59971</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87972</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313067</t>
+          <t>314832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>371801</t>
+          <t>374472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415835</t>
+          <t>417112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>467439</t>
+          <t>468810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>180072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207712</t>
+          <t>208513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608236</t>
+          <t>605565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666970</t>
+          <t>665205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80260</t>
+          <t>77920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110440</t>
+          <t>110335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>49308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75158</t>
+          <t>74178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>136787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177357</t>
+          <t>179683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107680</t>
+          <t>107785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137860</t>
+          <t>140200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122537</t>
+          <t>123517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148391</t>
+          <t>148387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238458</t>
+          <t>236132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278598</t>
+          <t>279028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43533</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43815</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69988</t>
+          <t>69336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76204</t>
+          <t>73459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107071</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48608</t>
+          <t>48873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130367</t>
+          <t>131019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168383</t>
+          <t>169983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199250</t>
+          <t>201995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566973</t>
+          <t>566907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>645433</t>
+          <t>644854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234697</t>
+          <t>233673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>290245</t>
+          <t>289839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>816244</t>
+          <t>818648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>916724</t>
+          <t>916174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1071244</t>
+          <t>1071823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1149704</t>
+          <t>1149770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>707045</t>
+          <t>707451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>762593</t>
+          <t>763617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1797243</t>
+          <t>1797793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1897723</t>
+          <t>1895319</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>70871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38731</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>102888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175338</t>
+          <t>177055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205231</t>
+          <t>205418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>105234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126234</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>289913</t>
+          <t>289910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>325972</t>
+          <t>324670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>48333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77694</t>
+          <t>77179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>33849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59089</t>
+          <t>58675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86931</t>
+          <t>87716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126108</t>
+          <t>126786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153963</t>
+          <t>154478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183663</t>
+          <t>183324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113498</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139379</t>
+          <t>138738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278136</t>
+          <t>277458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317313</t>
+          <t>316528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132768</t>
+          <t>134428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175311</t>
+          <t>176384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155821</t>
+          <t>156096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199177</t>
+          <t>199614</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230742</t>
+          <t>229669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273285</t>
+          <t>271625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82400</t>
+          <t>82163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>98922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320174</t>
+          <t>319737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363530</t>
+          <t>363255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>286006</t>
+          <t>280983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>343430</t>
+          <t>339051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92561</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129173</t>
+          <t>132029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387512</t>
+          <t>390356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>456453</t>
+          <t>459668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>435254</t>
+          <t>439633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492678</t>
+          <t>497701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260755</t>
+          <t>257899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297367</t>
+          <t>296842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712159</t>
+          <t>708944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>781100</t>
+          <t>778256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105677</t>
+          <t>106714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141607</t>
+          <t>142168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>68844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100524</t>
+          <t>101218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183593</t>
+          <t>181931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231635</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181180</t>
+          <t>180619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217110</t>
+          <t>216073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178525</t>
+          <t>177831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209922</t>
+          <t>210205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370201</t>
+          <t>369890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418243</t>
+          <t>419905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>31649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59134</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88043</t>
+          <t>88363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84058</t>
+          <t>83272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115304</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127552</t>
+          <t>127232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156461</t>
+          <t>156406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155517</t>
+          <t>155633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186763</t>
+          <t>187549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>687887</t>
+          <t>689156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>778300</t>
+          <t>782796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331582</t>
+          <t>330097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>400702</t>
+          <t>400422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1039695</t>
+          <t>1038852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151734</t>
+          <t>1150670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1264032</t>
+          <t>1259536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1354445</t>
+          <t>1353176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>914627</t>
+          <t>914907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>983747</t>
+          <t>985232</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2205927</t>
+          <t>2206991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2317966</t>
+          <t>2318809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61406</t>
+          <t>59525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93831</t>
+          <t>92001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136158</t>
+          <t>138039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162875</t>
+          <t>162890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89539</t>
+          <t>88942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109817</t>
+          <t>109236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233112</t>
+          <t>234942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265786</t>
+          <t>266220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48573</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76557</t>
+          <t>78970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111282</t>
+          <t>111337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101341</t>
+          <t>102302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127207</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115572</t>
+          <t>113668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>135072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223533</t>
+          <t>223478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258258</t>
+          <t>255845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105599</t>
+          <t>105396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140553</t>
+          <t>139896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120455</t>
+          <t>120344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159287</t>
+          <t>157404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174679</t>
+          <t>175336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209633</t>
+          <t>209836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53293</t>
+          <t>54915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220266</t>
+          <t>222149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259098</t>
+          <t>259209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217734</t>
+          <t>216857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265590</t>
+          <t>265454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81679</t>
+          <t>79296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>117473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309572</t>
+          <t>307941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>371088</t>
+          <t>372671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382067</t>
+          <t>382203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429923</t>
+          <t>430800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284842</t>
+          <t>284428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320222</t>
+          <t>322605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678469</t>
+          <t>676886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>739985</t>
+          <t>741616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119710</t>
+          <t>119578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157780</t>
+          <t>158932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110777</t>
+          <t>111042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210546</t>
+          <t>210531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258080</t>
+          <t>257653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196771</t>
+          <t>195619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234841</t>
+          <t>234973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171876</t>
+          <t>171611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204087</t>
+          <t>202579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379123</t>
+          <t>379550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426657</t>
+          <t>426672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>62048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95045</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53458</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141374</t>
+          <t>143878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167386</t>
+          <t>168976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186004</t>
+          <t>188401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215811</t>
+          <t>216521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>598173</t>
+          <t>603112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>680633</t>
+          <t>683872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>293267</t>
+          <t>292913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>355366</t>
+          <t>356536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>900368</t>
+          <t>910237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1011628</t>
+          <t>1017155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1085274</t>
+          <t>1082035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1167734</t>
+          <t>1162795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>887848</t>
+          <t>886678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>949947</t>
+          <t>950301</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1997493</t>
+          <t>1991966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2108753</t>
+          <t>2098884</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63876</t>
+          <t>63585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>92453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>141802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166767</t>
+          <t>168490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98288</t>
+          <t>98013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113745</t>
+          <t>113595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246728</t>
+          <t>245857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275891</t>
+          <t>275861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68653</t>
+          <t>70582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>46499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75179</t>
+          <t>76398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108446</t>
+          <t>108055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114891</t>
+          <t>112962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>141124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91716</t>
+          <t>92394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111506</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213991</t>
+          <t>214382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247258</t>
+          <t>246039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184287</t>
+          <t>184417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190193</t>
+          <t>190343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274612</t>
+          <t>274482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433605</t>
+          <t>433021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315282</t>
+          <t>315132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480401</t>
+          <t>472315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163014</t>
+          <t>164273</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211079</t>
+          <t>209928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90544</t>
+          <t>89355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233924</t>
+          <t>234490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286692</t>
+          <t>290565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311007</t>
+          <t>312158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359072</t>
+          <t>357813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>197198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222932</t>
+          <t>225724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521947</t>
+          <t>518074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574715</t>
+          <t>574149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83635</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116276</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133918</t>
+          <t>135158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173764</t>
+          <t>175534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129409</t>
+          <t>130378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162050</t>
+          <t>161988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158807</t>
+          <t>158027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182581</t>
+          <t>181093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297266</t>
+          <t>295496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337112</t>
+          <t>335872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>30746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>89663</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106769</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110402</t>
+          <t>107483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>133614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298535</t>
+          <t>285447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578752</t>
+          <t>580059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201816</t>
+          <t>201894</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248737</t>
+          <t>247724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>510272</t>
+          <t>518157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>794571</t>
+          <t>795979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1071251</t>
+          <t>1069944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1351468</t>
+          <t>1364556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>702554</t>
+          <t>703567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>749475</t>
+          <t>749397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1806723</t>
+          <t>1805315</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2091022</t>
+          <t>2083137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>56116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85252</t>
+          <t>85549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>152632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180431</t>
+          <t>180316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85160</t>
+          <t>85100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>100656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246449</t>
+          <t>246152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>276494</t>
+          <t>275585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40997</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66246</t>
+          <t>65723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>52443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110149</t>
+          <t>110238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119402</t>
+          <t>119925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144651</t>
+          <t>145041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107557</t>
+          <t>106134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>129507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234076</t>
+          <t>233987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269921</t>
+          <t>266965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88609</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120657</t>
+          <t>121943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98383</t>
+          <t>98038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134494</t>
+          <t>133954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>183787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>217121</t>
+          <t>216697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232241</t>
+          <t>232781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268352</t>
+          <t>268697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>243544</t>
+          <t>244093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295242</t>
+          <t>295179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59170</t>
+          <t>59265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87611</t>
+          <t>89252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>314832</t>
+          <t>312102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374472</t>
+          <t>372344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>417112</t>
+          <t>417175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>468810</t>
+          <t>468261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180072</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208513</t>
+          <t>208418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>605565</t>
+          <t>607693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>665205</t>
+          <t>667935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77920</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110335</t>
+          <t>110957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74178</t>
+          <t>77404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136787</t>
+          <t>137814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179683</t>
+          <t>179064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107785</t>
+          <t>107163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140200</t>
+          <t>136768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123517</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148387</t>
+          <t>147870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236132</t>
+          <t>236751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279028</t>
+          <t>278001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44378</t>
+          <t>43710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73459</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105471</t>
+          <t>105342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>48710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131019</t>
+          <t>132121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155977</t>
+          <t>156645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169983</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201995</t>
+          <t>200962</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566907</t>
+          <t>566303</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>644854</t>
+          <t>647342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233673</t>
+          <t>232670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289839</t>
+          <t>290600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>818648</t>
+          <t>821443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>916174</t>
+          <t>915733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1071823</t>
+          <t>1069335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1149770</t>
+          <t>1150374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>707451</t>
+          <t>706690</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>763617</t>
+          <t>764620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1797793</t>
+          <t>1798234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1895319</t>
+          <t>1892524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42508</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70871</t>
+          <t>70937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102888</t>
+          <t>103798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>176989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205418</t>
+          <t>204307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>103255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125639</t>
+          <t>125685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>289910</t>
+          <t>289000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>324670</t>
+          <t>325223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48333</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>79095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>58348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87716</t>
+          <t>89390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126786</t>
+          <t>126881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154478</t>
+          <t>152562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183324</t>
+          <t>182878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113912</t>
+          <t>114239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138738</t>
+          <t>139292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277458</t>
+          <t>277363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316528</t>
+          <t>314854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134428</t>
+          <t>136177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176384</t>
+          <t>175718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156096</t>
+          <t>156374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199614</t>
+          <t>198238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229669</t>
+          <t>230335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271625</t>
+          <t>269876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82163</t>
+          <t>81346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98922</t>
+          <t>99366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319737</t>
+          <t>321113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363255</t>
+          <t>362977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280983</t>
+          <t>283965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>339051</t>
+          <t>339703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93086</t>
+          <t>93735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132029</t>
+          <t>132228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390356</t>
+          <t>393348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459668</t>
+          <t>455535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>439633</t>
+          <t>438981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>497701</t>
+          <t>494719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257899</t>
+          <t>257700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296842</t>
+          <t>296193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708944</t>
+          <t>713077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778256</t>
+          <t>775264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106714</t>
+          <t>104559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142168</t>
+          <t>139831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68844</t>
+          <t>69079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101218</t>
+          <t>99991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181931</t>
+          <t>184116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231946</t>
+          <t>230768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180619</t>
+          <t>182956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216073</t>
+          <t>218228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177831</t>
+          <t>179058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210205</t>
+          <t>209970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369890</t>
+          <t>371068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419905</t>
+          <t>417720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88363</t>
+          <t>87572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83272</t>
+          <t>82981</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115188</t>
+          <t>115852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127232</t>
+          <t>128023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156406</t>
+          <t>155389</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155633</t>
+          <t>154969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187549</t>
+          <t>187840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>689156</t>
+          <t>688887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>782796</t>
+          <t>776648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>330097</t>
+          <t>331814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>400422</t>
+          <t>403981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1038852</t>
+          <t>1043181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1150670</t>
+          <t>1149846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1259536</t>
+          <t>1265684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1353176</t>
+          <t>1353445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>914907</t>
+          <t>911348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>985232</t>
+          <t>983515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2206991</t>
+          <t>2207815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2318809</t>
+          <t>2314480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59525</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92001</t>
+          <t>92734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138039</t>
+          <t>137170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162890</t>
+          <t>163008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88942</t>
+          <t>88877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109236</t>
+          <t>109294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234942</t>
+          <t>234209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266220</t>
+          <t>265789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47289</t>
+          <t>48621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73478</t>
+          <t>73072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78970</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111337</t>
+          <t>109568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102302</t>
+          <t>102708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128491</t>
+          <t>127159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>115460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135072</t>
+          <t>135919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223478</t>
+          <t>225247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255845</t>
+          <t>259479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105396</t>
+          <t>105604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139896</t>
+          <t>140293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120344</t>
+          <t>120916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157404</t>
+          <t>160327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175336</t>
+          <t>174939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209836</t>
+          <t>209628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54915</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222149</t>
+          <t>219226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259209</t>
+          <t>258637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216857</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265454</t>
+          <t>267698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79296</t>
+          <t>84439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117473</t>
+          <t>118839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>307941</t>
+          <t>309078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372671</t>
+          <t>370822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382203</t>
+          <t>379959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430800</t>
+          <t>428866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284428</t>
+          <t>283062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322605</t>
+          <t>317462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>676886</t>
+          <t>678735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>741616</t>
+          <t>740479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119578</t>
+          <t>119983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158932</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80074</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111042</t>
+          <t>110815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210531</t>
+          <t>210179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257653</t>
+          <t>260511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195619</t>
+          <t>196261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234973</t>
+          <t>234568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171611</t>
+          <t>171838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202579</t>
+          <t>204093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379550</t>
+          <t>376692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426672</t>
+          <t>427024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>62028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>65663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>96137</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53565</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143878</t>
+          <t>143898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168976</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188401</t>
+          <t>184912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216521</t>
+          <t>215386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>603112</t>
+          <t>598029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>683872</t>
+          <t>678638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292913</t>
+          <t>292915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>354513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>910237</t>
+          <t>907365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1017155</t>
+          <t>1009526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1082035</t>
+          <t>1087269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1162795</t>
+          <t>1167878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>886678</t>
+          <t>888701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>950301</t>
+          <t>950299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1991966</t>
+          <t>1999595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2098884</t>
+          <t>2101756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49731</t>
+          <t>51509</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>39608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63585</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76172</t>
+          <t>80403</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62449</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92453</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>155656</t>
+          <t>169839</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141802</t>
+          <t>155869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168490</t>
+          <t>181740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>106482</t>
+          <t>112297</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98013</t>
+          <t>103646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113595</t>
+          <t>119639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>262138</t>
+          <t>282135</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245857</t>
+          <t>265471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275861</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>205387</t>
+          <t>221348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205387</t>
+          <t>221348</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>205387</t>
+          <t>221348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132922</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132922</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132922</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>338310</t>
+          <t>362538</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338310</t>
+          <t>362538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>338310</t>
+          <t>362538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54331</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>68718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46499</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90932</t>
+          <t>94687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76398</t>
+          <t>79826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108055</t>
+          <t>110707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>129213</t>
+          <t>138624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112962</t>
+          <t>125916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141124</t>
+          <t>151773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>102292</t>
+          <t>114789</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92394</t>
+          <t>103872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111013</t>
+          <t>123013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>231505</t>
+          <t>253414</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214382</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246039</t>
+          <t>268275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183544</t>
+          <t>194634</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183544</t>
+          <t>194634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183544</t>
+          <t>194634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138893</t>
+          <t>153467</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138893</t>
+          <t>153467</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138893</t>
+          <t>153467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>322437</t>
+          <t>348101</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322437</t>
+          <t>348101</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>322437</t>
+          <t>348101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184417</t>
+          <t>100725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>93144</t>
+          <t>96740</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>82042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190343</t>
+          <t>113133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>376983</t>
+          <t>146818</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274482</t>
+          <t>131148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433021</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>412331</t>
+          <t>184419</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315132</t>
+          <t>168026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>472315</t>
+          <t>199117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>458899</t>
+          <t>231873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>458899</t>
+          <t>231873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>458899</t>
+          <t>231873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>505475</t>
+          <t>281159</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>505475</t>
+          <t>281159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>505475</t>
+          <t>281159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>186233</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164273</t>
+          <t>179230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209928</t>
+          <t>227193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75164</t>
+          <t>77463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>63848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89355</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>261398</t>
+          <t>280677</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234490</t>
+          <t>254483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290565</t>
+          <t>309356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>335853</t>
+          <t>365186</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312158</t>
+          <t>341207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357813</t>
+          <t>389170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>211389</t>
+          <t>232509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197198</t>
+          <t>217859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>246124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>547241</t>
+          <t>597695</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518074</t>
+          <t>569016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574149</t>
+          <t>623889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>522086</t>
+          <t>568400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>522086</t>
+          <t>568400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>522086</t>
+          <t>568400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>309972</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>309972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>309972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>808639</t>
+          <t>878372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>808639</t>
+          <t>878372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>808639</t>
+          <t>878372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>107884</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>92235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>126504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67318</t>
+          <t>72189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>153914</t>
+          <t>167173</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135158</t>
+          <t>147800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175534</t>
+          <t>187415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>146268</t>
+          <t>168892</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130378</t>
+          <t>150272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161988</t>
+          <t>184541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>170848</t>
+          <t>190796</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158027</t>
+          <t>177896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>201856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>317116</t>
+          <t>359687</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>339445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335872</t>
+          <t>379060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>245685</t>
+          <t>276776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>245685</t>
+          <t>276776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>245685</t>
+          <t>276776</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>225345</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225345</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225345</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>471030</t>
+          <t>526860</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>471030</t>
+          <t>526860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>471030</t>
+          <t>526860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>99228</t>
+          <t>104939</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89663</t>
+          <t>95625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>112235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>123588</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107483</t>
+          <t>115352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133614</t>
+          <t>136684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>127206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>127206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>127206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>155403</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155403</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155403</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>481671</t>
+          <t>512524</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>285447</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>580059</t>
+          <t>551915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>225703</t>
+          <t>238275</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201894</t>
+          <t>215601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>262541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>707375</t>
+          <t>750798</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>518157</t>
+          <t>707086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>795979</t>
+          <t>798506</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1168332</t>
+          <t>1012303</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1069944</t>
+          <t>972912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1364556</t>
+          <t>1050379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>725588</t>
+          <t>792932</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703567</t>
+          <t>768666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>749397</t>
+          <t>815606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1893919</t>
+          <t>1805236</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1805315</t>
+          <t>1757528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2083137</t>
+          <t>1848948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>72,34%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1650003</t>
+          <t>1524827</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1650003</t>
+          <t>1524827</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1650003</t>
+          <t>1524827</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>951291</t>
+          <t>1031207</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>951291</t>
+          <t>1031207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>951291</t>
+          <t>1031207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2601294</t>
+          <t>2556034</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2601294</t>
+          <t>2556034</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2601294</t>
+          <t>2556034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
